--- a/dev_Python/1. 업무/3. 공통업무/장비등록_양식.xlsx
+++ b/dev_Python/1. 업무/3. 공통업무/장비등록_양식.xlsx
@@ -1,50 +1,257 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\learning\dev_Python\1. 업무\3. 공통업무\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7395AD-A23E-4476-941D-A8701F095ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장비목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="장비목록" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="60">
+  <si>
+    <t>품명</t>
+  </si>
+  <si>
+    <t>모델명</t>
+  </si>
+  <si>
+    <t>관리번호</t>
+  </si>
+  <si>
+    <t>제조사</t>
+  </si>
+  <si>
+    <t>도입일</t>
+  </si>
+  <si>
+    <t>도입가</t>
+  </si>
+  <si>
+    <t>상태구분</t>
+  </si>
+  <si>
+    <t>도입처</t>
+  </si>
+  <si>
+    <t>용도및특이사항</t>
+  </si>
+  <si>
+    <t>주요성능및특징</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>원자흡광광도계</t>
+  </si>
+  <si>
+    <t>AA-7000</t>
+  </si>
+  <si>
+    <t>수질-001</t>
+  </si>
+  <si>
+    <t>Shimadzu</t>
+  </si>
+  <si>
+    <t>2024-03-15</t>
+  </si>
+  <si>
+    <t>신품</t>
+  </si>
+  <si>
+    <t>(예시) 시스템에 등록된 업체명</t>
+  </si>
+  <si>
+    <t>중금속 분석</t>
+  </si>
+  <si>
+    <t>불꽃/흑연로 겸용</t>
+  </si>
+  <si>
+    <t>예시 행 - 지우고 사용</t>
+  </si>
+  <si>
+    <t>AA-7001</t>
+  </si>
+  <si>
+    <t>수질-002</t>
+  </si>
+  <si>
+    <t>2024-03-16</t>
+  </si>
+  <si>
+    <t>AA-7002</t>
+  </si>
+  <si>
+    <t>수질-003</t>
+  </si>
+  <si>
+    <t>2024-03-17</t>
+  </si>
+  <si>
+    <t>AA-7003</t>
+  </si>
+  <si>
+    <t>수질-004</t>
+  </si>
+  <si>
+    <t>2024-03-18</t>
+  </si>
+  <si>
+    <t>AA-7004</t>
+  </si>
+  <si>
+    <t>수질-005</t>
+  </si>
+  <si>
+    <t>2024-03-19</t>
+  </si>
+  <si>
+    <t>AA-7005</t>
+  </si>
+  <si>
+    <t>수질-006</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>AA-7006</t>
+  </si>
+  <si>
+    <t>수질-007</t>
+  </si>
+  <si>
+    <t>2024-03-21</t>
+  </si>
+  <si>
+    <t>AA-7007</t>
+  </si>
+  <si>
+    <t>수질-008</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>AA-7008</t>
+  </si>
+  <si>
+    <t>수질-009</t>
+  </si>
+  <si>
+    <t>2024-03-23</t>
+  </si>
+  <si>
+    <t>AA-7009</t>
+  </si>
+  <si>
+    <t>수질-010</t>
+  </si>
+  <si>
+    <t>2024-03-24</t>
+  </si>
+  <si>
+    <t>AA-7010</t>
+  </si>
+  <si>
+    <t>수질-011</t>
+  </si>
+  <si>
+    <t>2024-03-25</t>
+  </si>
+  <si>
+    <t>AA-7011</t>
+  </si>
+  <si>
+    <t>수질-012</t>
+  </si>
+  <si>
+    <t>2024-03-26</t>
+  </si>
+  <si>
+    <t>AA-7012</t>
+  </si>
+  <si>
+    <t>수질-013</t>
+  </si>
+  <si>
+    <t>2024-03-27</t>
+  </si>
+  <si>
+    <t>AA-7013</t>
+  </si>
+  <si>
+    <t>수질-014</t>
+  </si>
+  <si>
+    <t>2024-03-28</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF888888"/>
       <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
+        <fgColor rgb="FF2E7D32"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,85 +268,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -427,140 +575,549 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>품명</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>모델명</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>관리번호</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>제조사</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>도입일</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>도입가</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>상태구분</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>도입처</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>용도및특이사항</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>주요성능및특징</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>원자흡광광도계</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>AA-7000</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>수질-001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Shimadzu</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3">
         <v>45000000</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>신품</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>(예시) 시스템에 등록된 업체명</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>중금속 분석</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>불꽃/흑연로 겸용</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>예시 행 - 지우고 사용</t>
-        </is>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3">
+        <v>45000001</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3">
+        <v>45000002</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3">
+        <v>45000003</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="3">
+        <v>45000004</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3">
+        <v>45000005</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>45000006</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="3">
+        <v>45000007</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3">
+        <v>45000008</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3">
+        <v>45000009</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3">
+        <v>45000010</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3">
+        <v>45000011</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="3">
+        <v>45000012</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3">
+        <v>45000013</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>